--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,1156 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122429214</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>563150</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7039277</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122429315</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563189</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7039266</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122429987</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>563292</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7039316</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122430372</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78646</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>563267</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7039412</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122430105</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>563336</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7039350</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122430072</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>563343</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7039325</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122430029</v>
+      </c>
+      <c r="B9" t="n">
+        <v>55974</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>563308</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7039306</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122429353</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>563199</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7039264</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122430232</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57374</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>563327</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7039349</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122429972</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79727</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Trollklippen, Trollklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>563297</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7039313</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122429214</v>
+        <v>122430232</v>
       </c>
       <c r="B3" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563150</v>
+        <v>563327</v>
       </c>
       <c r="R3" t="n">
-        <v>7039277</v>
+        <v>7039349</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1235,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122430105</v>
+        <v>122430029</v>
       </c>
       <c r="B7" t="n">
-        <v>79727</v>
+        <v>55974</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563336</v>
+        <v>563308</v>
       </c>
       <c r="R7" t="n">
-        <v>7039350</v>
+        <v>7039306</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122430072</v>
+        <v>122430105</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563343</v>
+        <v>563336</v>
       </c>
       <c r="R8" t="n">
-        <v>7039325</v>
+        <v>7039350</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,12 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122430029</v>
+        <v>122429972</v>
       </c>
       <c r="B9" t="n">
-        <v>55974</v>
+        <v>79727</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563308</v>
+        <v>563297</v>
       </c>
       <c r="R9" t="n">
-        <v>7039306</v>
+        <v>7039313</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122430232</v>
+        <v>122430072</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563327</v>
+        <v>563343</v>
       </c>
       <c r="R11" t="n">
-        <v>7039349</v>
+        <v>7039325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122429972</v>
+        <v>122429214</v>
       </c>
       <c r="B12" t="n">
         <v>79727</v>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563297</v>
+        <v>563150</v>
       </c>
       <c r="R12" t="n">
-        <v>7039313</v>
+        <v>7039277</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122430232</v>
+        <v>122429987</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563327</v>
+        <v>563292</v>
       </c>
       <c r="R3" t="n">
-        <v>7039349</v>
+        <v>7039316</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +902,7 @@
         <v>122429315</v>
       </c>
       <c r="B4" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429987</v>
+        <v>122430072</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563292</v>
+        <v>563343</v>
       </c>
       <c r="R5" t="n">
-        <v>7039316</v>
+        <v>7039325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122430372</v>
+        <v>122430029</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>55979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563267</v>
+        <v>563308</v>
       </c>
       <c r="R6" t="n">
-        <v>7039412</v>
+        <v>7039306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122430029</v>
+        <v>122430105</v>
       </c>
       <c r="B7" t="n">
-        <v>55974</v>
+        <v>79732</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563308</v>
+        <v>563336</v>
       </c>
       <c r="R7" t="n">
-        <v>7039306</v>
+        <v>7039350</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122430105</v>
+        <v>122429214</v>
       </c>
       <c r="B8" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563336</v>
+        <v>563150</v>
       </c>
       <c r="R8" t="n">
-        <v>7039350</v>
+        <v>7039277</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429972</v>
+        <v>122430232</v>
       </c>
       <c r="B9" t="n">
-        <v>79727</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,34 +1485,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563297</v>
+        <v>563327</v>
       </c>
       <c r="R9" t="n">
-        <v>7039313</v>
+        <v>7039349</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1559,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429353</v>
+        <v>122430372</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,39 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563199</v>
+        <v>563267</v>
       </c>
       <c r="R10" t="n">
-        <v>7039264</v>
+        <v>7039412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,12 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122430072</v>
+        <v>122429353</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563343</v>
+        <v>563199</v>
       </c>
       <c r="R11" t="n">
-        <v>7039325</v>
+        <v>7039264</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122429214</v>
+        <v>122429972</v>
       </c>
       <c r="B12" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563150</v>
+        <v>563297</v>
       </c>
       <c r="R12" t="n">
-        <v>7039277</v>
+        <v>7039313</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430072</v>
+        <v>122429353</v>
       </c>
       <c r="B5" t="n">
         <v>57379</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563343</v>
+        <v>563199</v>
       </c>
       <c r="R5" t="n">
-        <v>7039325</v>
+        <v>7039264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122430029</v>
+        <v>122429972</v>
       </c>
       <c r="B6" t="n">
-        <v>55979</v>
+        <v>79732</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563308</v>
+        <v>563297</v>
       </c>
       <c r="R6" t="n">
-        <v>7039306</v>
+        <v>7039313</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122430105</v>
+        <v>122430029</v>
       </c>
       <c r="B7" t="n">
-        <v>79732</v>
+        <v>55979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563336</v>
+        <v>563308</v>
       </c>
       <c r="R7" t="n">
-        <v>7039350</v>
+        <v>7039306</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122430372</v>
+        <v>122430105</v>
       </c>
       <c r="B10" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563267</v>
+        <v>563336</v>
       </c>
       <c r="R10" t="n">
-        <v>7039412</v>
+        <v>7039350</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429353</v>
+        <v>122430072</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563199</v>
+        <v>563343</v>
       </c>
       <c r="R11" t="n">
-        <v>7039264</v>
+        <v>7039325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122429972</v>
+        <v>122430372</v>
       </c>
       <c r="B12" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563297</v>
+        <v>563267</v>
       </c>
       <c r="R12" t="n">
-        <v>7039313</v>
+        <v>7039412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122429987</v>
+        <v>122430372</v>
       </c>
       <c r="B3" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,11 +805,6 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563292</v>
+        <v>563267</v>
       </c>
       <c r="R3" t="n">
-        <v>7039316</v>
+        <v>7039412</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429315</v>
+        <v>122430232</v>
       </c>
       <c r="B4" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563189</v>
+        <v>563327</v>
       </c>
       <c r="R4" t="n">
-        <v>7039266</v>
+        <v>7039349</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429353</v>
+        <v>122430072</v>
       </c>
       <c r="B5" t="n">
         <v>57379</v>
@@ -1029,11 +1029,6 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563199</v>
+        <v>563343</v>
       </c>
       <c r="R5" t="n">
-        <v>7039264</v>
+        <v>7039325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429972</v>
+        <v>122429987</v>
       </c>
       <c r="B6" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1144,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563297</v>
+        <v>563292</v>
       </c>
       <c r="R6" t="n">
-        <v>7039313</v>
+        <v>7039316</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122430029</v>
+        <v>122429214</v>
       </c>
       <c r="B7" t="n">
-        <v>55979</v>
+        <v>79733</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1251,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Skogshare</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563308</v>
+        <v>563150</v>
       </c>
       <c r="R7" t="n">
-        <v>7039306</v>
+        <v>7039277</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429214</v>
+        <v>122429315</v>
       </c>
       <c r="B8" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,11 +1360,6 @@
       <c r="E8" t="n">
         <v>6458</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -1397,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563150</v>
+        <v>563189</v>
       </c>
       <c r="R8" t="n">
-        <v>7039277</v>
+        <v>7039266</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122430232</v>
+        <v>122429353</v>
       </c>
       <c r="B9" t="n">
         <v>57379</v>
@@ -1487,11 +1467,6 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1514,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563327</v>
+        <v>563199</v>
       </c>
       <c r="R9" t="n">
-        <v>7039349</v>
+        <v>7039264</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1591,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122430105</v>
+        <v>122430029</v>
       </c>
       <c r="B10" t="n">
-        <v>79732</v>
+        <v>55979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1582,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>206004</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563336</v>
+        <v>563308</v>
       </c>
       <c r="R10" t="n">
-        <v>7039350</v>
+        <v>7039306</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122430072</v>
+        <v>122430105</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,39 +1689,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563343</v>
+        <v>563336</v>
       </c>
       <c r="R11" t="n">
-        <v>7039325</v>
+        <v>7039350</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122430372</v>
+        <v>122429972</v>
       </c>
       <c r="B12" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1796,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563267</v>
+        <v>563297</v>
       </c>
       <c r="R12" t="n">
-        <v>7039412</v>
+        <v>7039313</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1860,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122430372</v>
+        <v>122429214</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563267</v>
+        <v>563150</v>
       </c>
       <c r="R3" t="n">
-        <v>7039412</v>
+        <v>7039277</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122430232</v>
+        <v>122429972</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563327</v>
+        <v>563297</v>
       </c>
       <c r="R4" t="n">
-        <v>7039349</v>
+        <v>7039313</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>122430072</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,6 +1028,11 @@
       </c>
       <c r="E5" t="n">
         <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429987</v>
+        <v>122430372</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,6 +1151,11 @@
       <c r="E6" t="n">
         <v>6425</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1163,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563292</v>
+        <v>563267</v>
       </c>
       <c r="R6" t="n">
-        <v>7039316</v>
+        <v>7039412</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429214</v>
+        <v>122430232</v>
       </c>
       <c r="B7" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,29 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563150</v>
+        <v>563327</v>
       </c>
       <c r="R7" t="n">
-        <v>7039277</v>
+        <v>7039349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429315</v>
+        <v>122429987</v>
       </c>
       <c r="B8" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,16 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563189</v>
+        <v>563292</v>
       </c>
       <c r="R8" t="n">
-        <v>7039266</v>
+        <v>7039316</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429353</v>
+        <v>122430105</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,34 +1495,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563199</v>
+        <v>563336</v>
       </c>
       <c r="R9" t="n">
-        <v>7039264</v>
+        <v>7039350</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,12 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122430029</v>
+        <v>122429315</v>
       </c>
       <c r="B10" t="n">
-        <v>55979</v>
+        <v>79737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,16 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206004</v>
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563308</v>
+        <v>563189</v>
       </c>
       <c r="R10" t="n">
-        <v>7039306</v>
+        <v>7039266</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122430105</v>
+        <v>122429353</v>
       </c>
       <c r="B11" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,29 +1719,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563336</v>
+        <v>563199</v>
       </c>
       <c r="R11" t="n">
-        <v>7039350</v>
+        <v>7039264</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122429972</v>
+        <v>122430029</v>
       </c>
       <c r="B12" t="n">
-        <v>79733</v>
+        <v>55983</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,16 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>206004</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1815,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563297</v>
+        <v>563308</v>
       </c>
       <c r="R12" t="n">
-        <v>7039313</v>
+        <v>7039306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1860,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122429214</v>
+        <v>122430105</v>
       </c>
       <c r="B3" t="n">
         <v>79737</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563150</v>
+        <v>563336</v>
       </c>
       <c r="R3" t="n">
-        <v>7039277</v>
+        <v>7039350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429972</v>
+        <v>122430029</v>
       </c>
       <c r="B4" t="n">
-        <v>79737</v>
+        <v>55983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563297</v>
+        <v>563308</v>
       </c>
       <c r="R4" t="n">
-        <v>7039313</v>
+        <v>7039306</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122430372</v>
+        <v>122430232</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563267</v>
+        <v>563327</v>
       </c>
       <c r="R6" t="n">
-        <v>7039412</v>
+        <v>7039349</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122430232</v>
+        <v>122429972</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563327</v>
+        <v>563297</v>
       </c>
       <c r="R7" t="n">
-        <v>7039349</v>
+        <v>7039313</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429987</v>
+        <v>122430372</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563292</v>
+        <v>563267</v>
       </c>
       <c r="R8" t="n">
-        <v>7039316</v>
+        <v>7039412</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122430105</v>
+        <v>122429987</v>
       </c>
       <c r="B9" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563336</v>
+        <v>563292</v>
       </c>
       <c r="R9" t="n">
-        <v>7039350</v>
+        <v>7039316</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429353</v>
+        <v>122429214</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,39 +1719,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563199</v>
+        <v>563150</v>
       </c>
       <c r="R11" t="n">
-        <v>7039264</v>
+        <v>7039277</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122430029</v>
+        <v>122429353</v>
       </c>
       <c r="B12" t="n">
-        <v>55983</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,34 +1831,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563308</v>
+        <v>563199</v>
       </c>
       <c r="R12" t="n">
-        <v>7039306</v>
+        <v>7039264</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1905,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122430105</v>
+        <v>122430029</v>
       </c>
       <c r="B3" t="n">
-        <v>79737</v>
+        <v>55983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563336</v>
+        <v>563308</v>
       </c>
       <c r="R3" t="n">
-        <v>7039350</v>
+        <v>7039306</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122430029</v>
+        <v>122429987</v>
       </c>
       <c r="B4" t="n">
-        <v>55983</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563308</v>
+        <v>563292</v>
       </c>
       <c r="R4" t="n">
-        <v>7039306</v>
+        <v>7039316</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430072</v>
+        <v>122429315</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563343</v>
+        <v>563189</v>
       </c>
       <c r="R5" t="n">
-        <v>7039325</v>
+        <v>7039266</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122430232</v>
+        <v>122429214</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563327</v>
+        <v>563150</v>
       </c>
       <c r="R6" t="n">
-        <v>7039349</v>
+        <v>7039277</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1367,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122430372</v>
+        <v>122430232</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1363,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563267</v>
+        <v>563327</v>
       </c>
       <c r="R8" t="n">
-        <v>7039412</v>
+        <v>7039349</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1437,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429987</v>
+        <v>122430105</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563292</v>
+        <v>563336</v>
       </c>
       <c r="R9" t="n">
-        <v>7039316</v>
+        <v>7039350</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429315</v>
+        <v>122429353</v>
       </c>
       <c r="B10" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,34 +1597,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563189</v>
+        <v>563199</v>
       </c>
       <c r="R10" t="n">
-        <v>7039266</v>
+        <v>7039264</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1671,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429214</v>
+        <v>122430072</v>
       </c>
       <c r="B11" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,34 +1719,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563150</v>
+        <v>563343</v>
       </c>
       <c r="R11" t="n">
-        <v>7039277</v>
+        <v>7039325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122429353</v>
+        <v>122430372</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,39 +1841,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563199</v>
+        <v>563267</v>
       </c>
       <c r="R12" t="n">
-        <v>7039264</v>
+        <v>7039412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,12 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122430029</v>
+        <v>122430072</v>
       </c>
       <c r="B3" t="n">
-        <v>55983</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563308</v>
+        <v>563343</v>
       </c>
       <c r="R3" t="n">
-        <v>7039306</v>
+        <v>7039325</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429315</v>
+        <v>122430105</v>
       </c>
       <c r="B5" t="n">
         <v>79737</v>
@@ -1051,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563189</v>
+        <v>563336</v>
       </c>
       <c r="R5" t="n">
-        <v>7039266</v>
+        <v>7039350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429214</v>
+        <v>122429972</v>
       </c>
       <c r="B6" t="n">
         <v>79737</v>
@@ -1163,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563150</v>
+        <v>563297</v>
       </c>
       <c r="R6" t="n">
-        <v>7039277</v>
+        <v>7039313</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429972</v>
+        <v>122429315</v>
       </c>
       <c r="B7" t="n">
         <v>79737</v>
@@ -1275,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563297</v>
+        <v>563189</v>
       </c>
       <c r="R7" t="n">
-        <v>7039313</v>
+        <v>7039266</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122430232</v>
+        <v>122430372</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563327</v>
+        <v>563267</v>
       </c>
       <c r="R8" t="n">
-        <v>7039349</v>
+        <v>7039412</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,12 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122430105</v>
+        <v>122429214</v>
       </c>
       <c r="B9" t="n">
         <v>79737</v>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563336</v>
+        <v>563150</v>
       </c>
       <c r="R9" t="n">
-        <v>7039350</v>
+        <v>7039277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122430072</v>
+        <v>122430232</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563343</v>
+        <v>563327</v>
       </c>
       <c r="R11" t="n">
-        <v>7039325</v>
+        <v>7039349</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122430372</v>
+        <v>122430029</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>55983</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563267</v>
+        <v>563308</v>
       </c>
       <c r="R12" t="n">
-        <v>7039412</v>
+        <v>7039306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122430072</v>
+        <v>122429315</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563343</v>
+        <v>563189</v>
       </c>
       <c r="R3" t="n">
-        <v>7039325</v>
+        <v>7039266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429987</v>
+        <v>122430072</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563292</v>
+        <v>563343</v>
       </c>
       <c r="R4" t="n">
-        <v>7039316</v>
+        <v>7039325</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430105</v>
+        <v>122430372</v>
       </c>
       <c r="B5" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563336</v>
+        <v>563267</v>
       </c>
       <c r="R5" t="n">
-        <v>7039350</v>
+        <v>7039412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429972</v>
+        <v>122429987</v>
       </c>
       <c r="B6" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563297</v>
+        <v>563292</v>
       </c>
       <c r="R6" t="n">
-        <v>7039313</v>
+        <v>7039316</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429315</v>
+        <v>122429353</v>
       </c>
       <c r="B7" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1261,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563189</v>
+        <v>563199</v>
       </c>
       <c r="R7" t="n">
-        <v>7039266</v>
+        <v>7039264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122430372</v>
+        <v>122430232</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1383,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563267</v>
+        <v>563327</v>
       </c>
       <c r="R8" t="n">
-        <v>7039412</v>
+        <v>7039349</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122429214</v>
+        <v>122430105</v>
       </c>
       <c r="B9" t="n">
         <v>79737</v>
@@ -1509,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563150</v>
+        <v>563336</v>
       </c>
       <c r="R9" t="n">
-        <v>7039277</v>
+        <v>7039350</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429353</v>
+        <v>122429214</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,39 +1617,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563199</v>
+        <v>563150</v>
       </c>
       <c r="R10" t="n">
-        <v>7039264</v>
+        <v>7039277</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,12 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122430232</v>
+        <v>122429972</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,39 +1729,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563327</v>
+        <v>563297</v>
       </c>
       <c r="R11" t="n">
-        <v>7039349</v>
+        <v>7039313</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122429315</v>
+        <v>122430105</v>
       </c>
       <c r="B3" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563189</v>
+        <v>563336</v>
       </c>
       <c r="R3" t="n">
-        <v>7039266</v>
+        <v>7039350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122430072</v>
+        <v>122430372</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563343</v>
+        <v>563267</v>
       </c>
       <c r="R4" t="n">
-        <v>7039325</v>
+        <v>7039412</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430372</v>
+        <v>122430072</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563267</v>
+        <v>563343</v>
       </c>
       <c r="R5" t="n">
-        <v>7039412</v>
+        <v>7039325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429987</v>
+        <v>122429214</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563292</v>
+        <v>563150</v>
       </c>
       <c r="R6" t="n">
-        <v>7039316</v>
+        <v>7039277</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,7 +1248,7 @@
         <v>122429353</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>122430232</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122430105</v>
+        <v>122430029</v>
       </c>
       <c r="B9" t="n">
-        <v>79737</v>
+        <v>55984</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,21 +1505,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563336</v>
+        <v>563308</v>
       </c>
       <c r="R9" t="n">
-        <v>7039350</v>
+        <v>7039306</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429214</v>
+        <v>122429315</v>
       </c>
       <c r="B10" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563150</v>
+        <v>563189</v>
       </c>
       <c r="R10" t="n">
-        <v>7039277</v>
+        <v>7039266</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429972</v>
+        <v>122429987</v>
       </c>
       <c r="B11" t="n">
-        <v>79737</v>
+        <v>78657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563297</v>
+        <v>563292</v>
       </c>
       <c r="R11" t="n">
-        <v>7039313</v>
+        <v>7039316</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122430029</v>
+        <v>122429972</v>
       </c>
       <c r="B12" t="n">
-        <v>55983</v>
+        <v>79738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563308</v>
+        <v>563297</v>
       </c>
       <c r="R12" t="n">
-        <v>7039306</v>
+        <v>7039313</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -1601,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429315</v>
+        <v>122429987</v>
       </c>
       <c r="B10" t="n">
-        <v>79738</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,21 +1617,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563189</v>
+        <v>563292</v>
       </c>
       <c r="R10" t="n">
-        <v>7039266</v>
+        <v>7039316</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429987</v>
+        <v>122429972</v>
       </c>
       <c r="B11" t="n">
-        <v>78657</v>
+        <v>79738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563292</v>
+        <v>563297</v>
       </c>
       <c r="R11" t="n">
-        <v>7039316</v>
+        <v>7039313</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122429972</v>
+        <v>122429315</v>
       </c>
       <c r="B12" t="n">
         <v>79738</v>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563297</v>
+        <v>563189</v>
       </c>
       <c r="R12" t="n">
-        <v>7039313</v>
+        <v>7039266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>122430105</v>
       </c>
       <c r="B3" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122430372</v>
+        <v>122429214</v>
       </c>
       <c r="B4" t="n">
-        <v>78657</v>
+        <v>79741</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563267</v>
+        <v>563150</v>
       </c>
       <c r="R4" t="n">
-        <v>7039412</v>
+        <v>7039277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430072</v>
+        <v>122430372</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563343</v>
+        <v>563267</v>
       </c>
       <c r="R5" t="n">
-        <v>7039325</v>
+        <v>7039412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429214</v>
+        <v>122429315</v>
       </c>
       <c r="B6" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563150</v>
+        <v>563189</v>
       </c>
       <c r="R6" t="n">
-        <v>7039277</v>
+        <v>7039266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429353</v>
+        <v>122430072</v>
       </c>
       <c r="B7" t="n">
         <v>57384</v>
@@ -1290,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563199</v>
+        <v>563343</v>
       </c>
       <c r="R7" t="n">
-        <v>7039264</v>
+        <v>7039325</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1325,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122430232</v>
+        <v>122429987</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563327</v>
+        <v>563292</v>
       </c>
       <c r="R8" t="n">
-        <v>7039349</v>
+        <v>7039316</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122430029</v>
+        <v>122429353</v>
       </c>
       <c r="B9" t="n">
-        <v>55984</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,34 +1485,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563308</v>
+        <v>563199</v>
       </c>
       <c r="R9" t="n">
-        <v>7039306</v>
+        <v>7039264</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1559,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122429987</v>
+        <v>122430232</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,34 +1607,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563292</v>
+        <v>563327</v>
       </c>
       <c r="R10" t="n">
-        <v>7039316</v>
+        <v>7039349</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1681,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122429972</v>
+        <v>122430029</v>
       </c>
       <c r="B11" t="n">
-        <v>79738</v>
+        <v>55984</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563297</v>
+        <v>563308</v>
       </c>
       <c r="R11" t="n">
-        <v>7039313</v>
+        <v>7039306</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122429315</v>
+        <v>122429972</v>
       </c>
       <c r="B12" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563189</v>
+        <v>563297</v>
       </c>
       <c r="R12" t="n">
-        <v>7039266</v>
+        <v>7039313</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122430105</v>
+        <v>122430029</v>
       </c>
       <c r="B3" t="n">
-        <v>79741</v>
+        <v>55984</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563336</v>
+        <v>563308</v>
       </c>
       <c r="R3" t="n">
-        <v>7039350</v>
+        <v>7039306</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429214</v>
+        <v>122429972</v>
       </c>
       <c r="B4" t="n">
         <v>79741</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563150</v>
+        <v>563297</v>
       </c>
       <c r="R4" t="n">
-        <v>7039277</v>
+        <v>7039313</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122430372</v>
+        <v>122430105</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
+        <v>79741</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563267</v>
+        <v>563336</v>
       </c>
       <c r="R5" t="n">
-        <v>7039412</v>
+        <v>7039350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429315</v>
+        <v>122430232</v>
       </c>
       <c r="B6" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1139,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563189</v>
+        <v>563327</v>
       </c>
       <c r="R6" t="n">
-        <v>7039266</v>
+        <v>7039349</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1357,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429987</v>
+        <v>122429315</v>
       </c>
       <c r="B8" t="n">
-        <v>78660</v>
+        <v>79741</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563292</v>
+        <v>563189</v>
       </c>
       <c r="R8" t="n">
-        <v>7039316</v>
+        <v>7039266</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1591,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122430232</v>
+        <v>122429214</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,39 +1617,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563327</v>
+        <v>563150</v>
       </c>
       <c r="R10" t="n">
-        <v>7039349</v>
+        <v>7039277</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,12 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122430029</v>
+        <v>122429987</v>
       </c>
       <c r="B11" t="n">
-        <v>55984</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563308</v>
+        <v>563292</v>
       </c>
       <c r="R11" t="n">
-        <v>7039306</v>
+        <v>7039316</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122429972</v>
+        <v>122430372</v>
       </c>
       <c r="B12" t="n">
-        <v>79741</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563297</v>
+        <v>563267</v>
       </c>
       <c r="R12" t="n">
-        <v>7039313</v>
+        <v>7039412</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 46629-2022 artfynd.xlsx
+++ b/artfynd/A 46629-2022 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122430072</v>
+        <v>122429315</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563343</v>
+        <v>563189</v>
       </c>
       <c r="R7" t="n">
-        <v>7039325</v>
+        <v>7039266</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429315</v>
+        <v>122430072</v>
       </c>
       <c r="B8" t="n">
-        <v>79741</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1373,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trollklippen, Trollklippen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563189</v>
+        <v>563343</v>
       </c>
       <c r="R8" t="n">
-        <v>7039266</v>
+        <v>7039325</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
